--- a/наброски/Координаты рабочих мест.xlsx
+++ b/наброски/Координаты рабочих мест.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MainUser\Desktop\hackaton\наброски\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MainUser\Desktop\hackathon-quantorium-2026\наброски\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D60A339-A1DA-454B-AF80-3F7E3570FAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD15F76-E98B-48E6-9E98-4E1FD89CC30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" activeTab="1" xr2:uid="{A80E890B-A276-400D-879B-71F621DE9F54}"/>
+    <workbookView xWindow="29055" yWindow="0" windowWidth="9345" windowHeight="21000" activeTab="1" xr2:uid="{A80E890B-A276-400D-879B-71F621DE9F54}"/>
   </bookViews>
   <sheets>
     <sheet name="1 этаж" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>Кабинет</t>
   </si>
@@ -35,6 +35,12 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -80,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,6 +96,9 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -600,13 +609,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B421A8-F082-4325-B68A-9C8E19C9E773}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,8 +625,20 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>201</v>
       </c>
@@ -627,8 +648,22 @@
       <c r="C2" s="2">
         <v>140</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" s="2">
+        <v>364</v>
+      </c>
+      <c r="F2" s="2">
+        <v>104</v>
+      </c>
+      <c r="G2">
+        <f>606-E2</f>
+        <v>242</v>
+      </c>
+      <c r="H2">
+        <f>209-F2</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>400</v>
       </c>
@@ -636,7 +671,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>465</v>
       </c>
@@ -644,7 +679,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>465</v>
       </c>
@@ -652,7 +687,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>500</v>
       </c>
@@ -660,7 +695,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>500</v>
       </c>
@@ -668,7 +703,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>202</v>
       </c>
@@ -678,8 +713,22 @@
       <c r="C8" s="2">
         <v>170</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E8" s="2">
+        <v>670</v>
+      </c>
+      <c r="F8" s="2">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <f>758-E8</f>
+        <v>88</v>
+      </c>
+      <c r="H8">
+        <f>246-F8</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>715</v>
       </c>
@@ -687,7 +736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>203</v>
       </c>
@@ -697,8 +746,22 @@
       <c r="C10" s="2">
         <v>265</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E10" s="2">
+        <v>485</v>
+      </c>
+      <c r="F10" s="2">
+        <v>209</v>
+      </c>
+      <c r="G10">
+        <f>606-E10</f>
+        <v>121</v>
+      </c>
+      <c r="H10">
+        <f>317-F10</f>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>570</v>
       </c>
@@ -706,7 +769,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>204</v>
       </c>
@@ -716,8 +779,22 @@
       <c r="C12" s="2">
         <v>350</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E12" s="2">
+        <v>670</v>
+      </c>
+      <c r="F12" s="2">
+        <v>246</v>
+      </c>
+      <c r="G12">
+        <f>758-E12</f>
+        <v>88</v>
+      </c>
+      <c r="H12">
+        <f>458-F12</f>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>715</v>
       </c>
